--- a/test/session--empty-statements/reference/1 semester 14 subjects/I семестр/25-4/Відомості 25-4.xlsx
+++ b/test/session--empty-statements/reference/1 semester 14 subjects/I семестр/25-4/Відомості 25-4.xlsx
@@ -23,7 +23,7 @@
     <definedName name="Ф80" localSheetId="2">#REF!</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Зведена G5'!$C$3:$S$30</definedName>
   </definedNames>
-  <calcPr calcId="191029" calcMode="autoNoTable" fullCalcOnLoad="1"/>
+  <calcPr calcId="152511" calcMode="autoNoTable" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -2888,7 +2888,7 @@
         </is>
       </c>
       <c r="F47" s="63">
-        <f>IF(F44="Очікую","Очікую",IF(F44-COUNTIF($T$10:$T38," - ")&lt;ROUNDDOWN(F44*0.4,0),F44-COUNTIF($T$10:$T38," - "),ROUNDDOWN(F44*0.4,0)))</f>
+        <f>IF(F44="Очікую","Очікую",IF(F44-COUNTIF($T$10:$T38," - ")&lt;ROUNDDOWN(F44*0.45,0),F44-COUNTIF($T$10:$T38," - "),ROUNDDOWN(F44*0.45,0)))</f>
         <v/>
       </c>
       <c r="G47" s="6" t="n"/>
@@ -2906,7 +2906,7 @@
       <c r="O47" s="54" t="n"/>
       <c r="P47" s="54" t="inlineStr">
         <is>
-          <t>Margarita BRITIKOVA</t>
+          <t>Маргарита БРІТІКОВА</t>
         </is>
       </c>
       <c r="Q47" s="54" t="n"/>
@@ -3196,7 +3196,7 @@
       <c r="B5" s="12" t="n"/>
       <c r="C5" s="73" t="inlineStr">
         <is>
-          <t>Успішності студентів спеціальності G3 ««Електрична інженерія»»</t>
+          <t>Успішності студентів спеціальності G3 «Електрична інженерія»</t>
         </is>
       </c>
       <c r="D5" s="92" t="n"/>
@@ -5078,7 +5078,7 @@
         </is>
       </c>
       <c r="F35" s="63">
-        <f>IF(F32="Очікую","Очікую",IF(F32-COUNTIF($T$10:$T26," - ")&lt;ROUNDDOWN(F32*0.4,0),F32-COUNTIF($T$10:$T26," - "),ROUNDDOWN(F32*0.4,0)))</f>
+        <f>IF(F32="Очікую","Очікую",IF(F32-COUNTIF($T$10:$T26," - ")&lt;ROUNDDOWN(F32*0.45,0),F32-COUNTIF($T$10:$T26," - "),ROUNDDOWN(F32*0.45,0)))</f>
         <v/>
       </c>
       <c r="G35" s="6" t="n"/>
@@ -5096,7 +5096,7 @@
       <c r="O35" s="56" t="n"/>
       <c r="P35" s="54" t="inlineStr">
         <is>
-          <t>Margarita BRITIKOVA</t>
+          <t>Маргарита БРІТІКОВА</t>
         </is>
       </c>
       <c r="Q35" s="54" t="n"/>
@@ -5402,7 +5402,7 @@
       <c r="B5" s="12" t="n"/>
       <c r="C5" s="73" t="inlineStr">
         <is>
-          <t>Успішності студентів спеціальності G5 ««Електроніка, електронні комунікації, приладобудування та радіотехніка»»</t>
+          <t>Успішності студентів спеціальності G5 «Електроніка, електронні комунікації, приладобудування та радіотехніка»</t>
         </is>
       </c>
       <c r="D5" s="92" t="n"/>
@@ -6899,7 +6899,7 @@
         </is>
       </c>
       <c r="F30" s="63">
-        <f>IF(F27="Очікую","Очікую",IF(F27-COUNTIF($T$10:$T21," - ")&lt;ROUNDDOWN(F27*0.4,0),F27-COUNTIF($T$10:$T21," - "),ROUNDDOWN(F27*0.4,0)))</f>
+        <f>IF(F27="Очікую","Очікую",IF(F27-COUNTIF($T$10:$T21," - ")&lt;ROUNDDOWN(F27*0.45,0),F27-COUNTIF($T$10:$T21," - "),ROUNDDOWN(F27*0.45,0)))</f>
         <v/>
       </c>
       <c r="G30" s="6" t="n"/>
@@ -6917,7 +6917,7 @@
       <c r="O30" s="56" t="n"/>
       <c r="P30" s="54" t="inlineStr">
         <is>
-          <t>Margarita BRITIKOVA</t>
+          <t>Маргарита БРІТІКОВА</t>
         </is>
       </c>
       <c r="Q30" s="54" t="n"/>
